--- a/output/Muster_Honorarrechnung-Lehrkräfte_March.xlsx
+++ b/output/Muster_Honorarrechnung-Lehrkräfte_March.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Rechnungsvorlage Honorar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$74</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3828125" defaultRowHeight="14.15" outlineLevelCol="0"/>
   <cols>
     <col width="15.07421875" customWidth="1" style="1" min="1" max="1"/>
@@ -984,7 +984,7 @@
       <c r="B24" s="18" t="n"/>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>31.03.2026 bis 31.03.2026</t>
+          <t>01.03.2026 bis 31.03.2026</t>
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
@@ -1058,15 +1058,15 @@
     <row r="32">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>31.03.2026</t>
+          <t>01.03.2026</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Unterricht ASA 8 Vertretung</t>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
@@ -1078,340 +1078,706 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="44" t="n"/>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="16" t="n"/>
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>02.03.2026</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 9 Vertretung</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E33" s="37">
         <f>ROUND(B33*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="44" t="n"/>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="16" t="n"/>
+      <c r="A34" s="44" t="inlineStr">
+        <is>
+          <t>02.03.2026</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E34" s="37">
         <f>ROUND(B34*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="44" t="n"/>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="26" t="n"/>
-      <c r="D35" s="16" t="n"/>
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>03.03.2026</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8 Vertretung</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E35" s="37">
         <f>ROUND(B35*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="44" t="n"/>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="16" t="n"/>
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E36" s="37">
         <f>ROUND(B36*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="44" t="n"/>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="26" t="n"/>
-      <c r="D37" s="16" t="n"/>
+      <c r="A37" s="44" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E37" s="37">
         <f>ROUND(B37*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="44" t="n"/>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="26" t="n"/>
-      <c r="D38" s="16" t="n"/>
+      <c r="A38" s="44" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E38" s="37">
         <f>ROUND(B38*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="44" t="n"/>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="26" t="n"/>
-      <c r="D39" s="16" t="n"/>
+      <c r="A39" s="44" t="inlineStr">
+        <is>
+          <t>06.03.2026</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8 Vertretung</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E39" s="37">
         <f>ROUND(B39*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="44" t="n"/>
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="16" t="n"/>
+      <c r="A40" s="44" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Vorbereitung Unterricht für 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E40" s="37">
         <f>ROUND(B40*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="44" t="n"/>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="15" t="n"/>
-      <c r="D41" s="16" t="n"/>
+      <c r="A41" s="44" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 9 Vertretung</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E41" s="37">
         <f>ROUND(B41*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="44" t="n"/>
-      <c r="B42" s="17" t="n"/>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="16" t="n"/>
+      <c r="A42" s="44" t="inlineStr">
+        <is>
+          <t>11.03.2026</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E42" s="37">
         <f>ROUND(B42*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="44" t="n"/>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="15" t="n"/>
-      <c r="D43" s="16" t="n"/>
+      <c r="A43" s="44" t="inlineStr">
+        <is>
+          <t>12.03.2026</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E43" s="37">
         <f>ROUND(B43*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="44" t="n"/>
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="15" t="n"/>
-      <c r="D44" s="16" t="n"/>
+      <c r="A44" s="44" t="inlineStr">
+        <is>
+          <t>12.03.2026</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E44" s="37">
         <f>ROUND(B44*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="44" t="n"/>
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="15" t="n"/>
-      <c r="D45" s="16" t="n"/>
+      <c r="A45" s="44" t="inlineStr">
+        <is>
+          <t>13.03.2026</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8 Vertretung</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E45" s="37">
         <f>ROUND(B45*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="44" t="n"/>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="15" t="n"/>
-      <c r="D46" s="16" t="n"/>
+      <c r="A46" s="44" t="inlineStr">
+        <is>
+          <t>18.03.2026</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E46" s="37">
         <f>ROUND(B46*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="44" t="n"/>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="15" t="n"/>
-      <c r="D47" s="16" t="n"/>
+      <c r="A47" s="44" t="inlineStr">
+        <is>
+          <t>19.03.2026</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>19</v>
+      </c>
       <c r="E47" s="37">
         <f>ROUND(B47*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="44" t="n"/>
-      <c r="B48" s="21" t="n"/>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="23" t="n"/>
+      <c r="A48" s="44" t="inlineStr">
+        <is>
+          <t>19.03.2026</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="n">
+        <v>19</v>
+      </c>
       <c r="E48" s="37">
         <f>ROUND(B48*$D$32,2)</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="14.6" customFormat="1" customHeight="1" s="7" thickBot="1">
-      <c r="A49" s="50" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="44" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8 Vertretung</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E49" s="37">
+        <f>ROUND(B49*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="44" t="inlineStr">
+        <is>
+          <t>23.03.2026</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E50" s="37">
+        <f>ROUND(B50*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="44" t="inlineStr">
+        <is>
+          <t>24.03.2026</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8 Vertretung</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E51" s="37">
+        <f>ROUND(B51*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="inlineStr">
+        <is>
+          <t>25.03.2026</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E52" s="37">
+        <f>ROUND(B52*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="inlineStr">
+        <is>
+          <t>26.03.2026</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E53" s="37">
+        <f>ROUND(B53*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="44" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E54" s="37">
+        <f>ROUND(B54*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="44" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8 Vertretung</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E55" s="37">
+        <f>ROUND(B55*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="44" t="n"/>
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="23" t="n"/>
+      <c r="E56" s="37">
+        <f>ROUND(B56*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="44" t="n"/>
+      <c r="B57" s="21" t="n"/>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="23" t="n"/>
+      <c r="E57" s="37">
+        <f>ROUND(B57*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="14.6" customFormat="1" customHeight="1" s="7" thickBot="1">
+      <c r="A58" s="50" t="inlineStr">
         <is>
           <t>Gesamtbetrag</t>
         </is>
       </c>
-      <c r="B49" s="56" t="n"/>
-      <c r="C49" s="56" t="n"/>
-      <c r="D49" s="24" t="n"/>
-      <c r="E49" s="38">
-        <f>SUM(E32:E48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="14.25" customHeight="1" thickTop="1">
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="8" t="n"/>
-      <c r="G50" s="8" t="n"/>
-      <c r="H50" s="9" t="n"/>
-      <c r="I50" s="9" t="n"/>
-    </row>
-    <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="B58" s="56" t="n"/>
+      <c r="C58" s="56" t="n"/>
+      <c r="D58" s="24" t="n"/>
+      <c r="E58" s="38">
+        <f>SUM(E32:E57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="14.25" customHeight="1" thickTop="1">
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="12" t="n"/>
+      <c r="E59" s="13" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="9" t="n"/>
+      <c r="I59" s="9" t="n"/>
+    </row>
+    <row r="60" ht="14.25" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Ich bitte um Überweisung des vorgenannten Rechnungsbetrages innerhalb von 14 Tagen.</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="14" t="n"/>
-      <c r="D51" s="14" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
-    </row>
-    <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="14" t="n"/>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="14" t="n"/>
+      <c r="D60" s="14" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="14.25" customHeight="1">
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="14" t="n"/>
+      <c r="D61" s="14" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t>Bank:</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="39" t="inlineStr">
+      <c r="B62" s="20" t="n"/>
+      <c r="C62" s="39" t="inlineStr">
         <is>
           <t>SumUp Limited</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n"/>
-      <c r="G53" s="3" t="n"/>
-      <c r="H53" s="3" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
         <is>
           <t>IBAN:</t>
         </is>
       </c>
-      <c r="B54" s="20" t="n"/>
-      <c r="C54" s="40" t="inlineStr">
+      <c r="B63" s="20" t="n"/>
+      <c r="C63" s="40" t="inlineStr">
         <is>
           <t>IE66SUMU99036512650081</t>
         </is>
       </c>
-      <c r="D54" s="12" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="D63" s="12" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="6" t="n"/>
+      <c r="G63" s="6" t="n"/>
+      <c r="H63" s="3" t="n"/>
+      <c r="I63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t>Kontoinhaber:in:</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="41" t="inlineStr">
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="41" t="inlineStr">
         <is>
           <t>Dominik Ballentin</t>
         </is>
       </c>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="6" t="n"/>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="54" t="n"/>
-      <c r="E56" s="57" t="n"/>
-      <c r="F56" s="6" t="n"/>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-    </row>
-    <row r="57">
-      <c r="D57" s="53" t="inlineStr">
+      <c r="D64" s="12" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="6" t="n"/>
+      <c r="H64" s="3" t="n"/>
+      <c r="I64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="54" t="n"/>
+      <c r="E65" s="57" t="n"/>
+      <c r="F65" s="6" t="n"/>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="53" t="inlineStr">
         <is>
           <t>Unterschrift Honorarkraft</t>
         </is>
       </c>
-      <c r="F57" s="6" t="n"/>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-    </row>
-    <row r="58">
-      <c r="D58" s="53" t="n"/>
-      <c r="E58" s="53" t="n"/>
-      <c r="F58" s="6" t="n"/>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="n"/>
-    </row>
-    <row r="59">
-      <c r="D59" s="53" t="n"/>
-      <c r="E59" s="53" t="n"/>
-      <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="3" t="n"/>
-      <c r="I59" s="3" t="n"/>
-    </row>
-    <row r="60">
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
-    </row>
-    <row r="61">
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="1" t="n"/>
-      <c r="E61" s="12" t="n"/>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="32" t="n"/>
-      <c r="B62" s="32" t="n"/>
-      <c r="C62" s="11" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="34" t="inlineStr">
+      <c r="F66" s="6" t="n"/>
+      <c r="G66" s="6" t="n"/>
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="D67" s="53" t="n"/>
+      <c r="E67" s="53" t="n"/>
+      <c r="F67" s="6" t="n"/>
+      <c r="G67" s="6" t="n"/>
+      <c r="H67" s="3" t="n"/>
+      <c r="I67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="D68" s="53" t="n"/>
+      <c r="E68" s="53" t="n"/>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="6" t="n"/>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="D69" s="53" t="n"/>
+      <c r="E69" s="53" t="n"/>
+      <c r="F69" s="6" t="n"/>
+      <c r="G69" s="6" t="n"/>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="1" t="n"/>
+      <c r="E70" s="12" t="n"/>
+      <c r="F70" s="6" t="n"/>
+      <c r="G70" s="6" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="32" t="n"/>
+      <c r="B71" s="32" t="n"/>
+      <c r="C71" s="11" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="34" t="inlineStr">
         <is>
           <t>sachlich und rechnerisch richtig</t>
         </is>
       </c>
-      <c r="B63" s="34" t="n"/>
-      <c r="C63" s="34" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="42" t="inlineStr">
+      <c r="B72" s="34" t="n"/>
+      <c r="C72" s="34" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="42" t="inlineStr">
         <is>
           <t>Unterschrift MA Pro Beruf GmbH</t>
         </is>
@@ -1422,10 +1788,10 @@
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="G10:I10"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D56:E56"/>
     <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D65:E65"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>

--- a/output/Muster_Honorarrechnung-Lehrkräfte_March.xlsx
+++ b/output/Muster_Honorarrechnung-Lehrkräfte_March.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="497" windowWidth="22149" windowHeight="12600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rechnungsvorlage Honorar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$74</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$75</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -212,7 +212,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -349,9 +349,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -756,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3828125" defaultRowHeight="14.15" outlineLevelCol="0"/>
   <cols>
     <col width="15.07421875" customWidth="1" style="1" min="1" max="1"/>
@@ -806,7 +803,7 @@
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="10" t="n"/>
       <c r="E3" s="10" t="n"/>
-      <c r="I3" s="55" t="n"/>
+      <c r="I3" s="54" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="45" t="inlineStr">
@@ -989,7 +986,7 @@
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
-      <c r="G24" s="55" t="n"/>
+      <c r="G24" s="54" t="n"/>
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="C25" s="4" t="n"/>
@@ -1366,7 +1363,7 @@
     <row r="46">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>18.03.2026</t>
+          <t>16.03.2026</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
@@ -1374,7 +1371,7 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+          <t>Vorbereitung für Unterricht 0,75 Stunden</t>
         </is>
       </c>
       <c r="D46" s="16" t="n">
@@ -1388,7 +1385,7 @@
     <row r="47">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>19.03.2026</t>
+          <t>17.03.2026</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
@@ -1396,7 +1393,7 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Unterricht ASA 8</t>
+          <t>Unterricht ASA 9 Vertretung</t>
         </is>
       </c>
       <c r="D47" s="16" t="n">
@@ -1410,7 +1407,7 @@
     <row r="48">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>19.03.2026</t>
+          <t>18.03.2026</t>
         </is>
       </c>
       <c r="B48" s="21" t="n">
@@ -1432,7 +1429,7 @@
     <row r="49">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>20.03.2026</t>
+          <t>19.03.2026</t>
         </is>
       </c>
       <c r="B49" s="21" t="n">
@@ -1440,7 +1437,7 @@
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>Unterricht ASA 8 Vertretung</t>
+          <t>Unterricht ASA 8</t>
         </is>
       </c>
       <c r="D49" s="23" t="n">
@@ -1454,7 +1451,7 @@
     <row r="50">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>23.03.2026</t>
+          <t>19.03.2026</t>
         </is>
       </c>
       <c r="B50" s="21" t="n">
@@ -1476,7 +1473,7 @@
     <row r="51">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>24.03.2026</t>
+          <t>20.03.2026</t>
         </is>
       </c>
       <c r="B51" s="21" t="n">
@@ -1498,7 +1495,7 @@
     <row r="52">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>25.03.2026</t>
+          <t>23.03.2026</t>
         </is>
       </c>
       <c r="B52" s="21" t="n">
@@ -1520,7 +1517,7 @@
     <row r="53">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>26.03.2026</t>
+          <t>24.03.2026</t>
         </is>
       </c>
       <c r="B53" s="21" t="n">
@@ -1528,7 +1525,7 @@
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Unterricht ASA 8</t>
+          <t>Unterricht ASA 8 Vertretung</t>
         </is>
       </c>
       <c r="D53" s="23" t="n">
@@ -1542,7 +1539,7 @@
     <row r="54">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>30.03.2026</t>
+          <t>25.03.2026</t>
         </is>
       </c>
       <c r="B54" s="21" t="n">
@@ -1564,7 +1561,7 @@
     <row r="55">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>31.03.2026</t>
+          <t>26.03.2026</t>
         </is>
       </c>
       <c r="B55" s="21" t="n">
@@ -1572,7 +1569,7 @@
       </c>
       <c r="C55" s="22" t="inlineStr">
         <is>
-          <t>Unterricht ASA 8 Vertretung</t>
+          <t>Unterricht ASA 8</t>
         </is>
       </c>
       <c r="D55" s="23" t="n">
@@ -1584,214 +1581,250 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="44" t="n"/>
-      <c r="B56" s="21" t="n"/>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="23" t="n"/>
+      <c r="A56" s="44" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>19</v>
+      </c>
       <c r="E56" s="37">
         <f>ROUND(B56*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="44" t="n"/>
-      <c r="B57" s="21" t="n"/>
-      <c r="C57" s="22" t="n"/>
-      <c r="D57" s="23" t="n"/>
+      <c r="A57" s="44" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="22" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8 Vertretung</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>19</v>
+      </c>
       <c r="E57" s="37">
         <f>ROUND(B57*$D$32,2)</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="14.6" customFormat="1" customHeight="1" s="7" thickBot="1">
-      <c r="A58" s="50" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="44" t="n"/>
+      <c r="B58" s="21" t="n"/>
+      <c r="C58" s="22" t="n"/>
+      <c r="D58" s="23" t="n"/>
+      <c r="E58" s="37">
+        <f>ROUND(B58*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="n"/>
+      <c r="B59" s="21" t="n"/>
+      <c r="C59" s="22" t="n"/>
+      <c r="D59" s="23" t="n"/>
+      <c r="E59" s="37">
+        <f>ROUND(B59*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="44" t="n"/>
+      <c r="B60" s="21" t="n"/>
+      <c r="C60" s="22" t="n"/>
+      <c r="D60" s="23" t="n"/>
+      <c r="E60" s="37">
+        <f>ROUND(B60*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="44" t="n"/>
+      <c r="B61" s="21" t="n"/>
+      <c r="C61" s="22" t="n"/>
+      <c r="D61" s="23" t="n"/>
+      <c r="E61" s="37">
+        <f>ROUND(B61*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="14.6" customFormat="1" customHeight="1" s="7" thickBot="1">
+      <c r="A62" s="50" t="inlineStr">
         <is>
           <t>Gesamtbetrag</t>
         </is>
       </c>
-      <c r="B58" s="56" t="n"/>
-      <c r="C58" s="56" t="n"/>
-      <c r="D58" s="24" t="n"/>
-      <c r="E58" s="38">
-        <f>SUM(E32:E57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="14.25" customHeight="1" thickTop="1">
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="13" t="n"/>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="9" t="n"/>
-      <c r="I59" s="9" t="n"/>
-    </row>
-    <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="B62" s="55" t="n"/>
+      <c r="C62" s="55" t="n"/>
+      <c r="D62" s="24" t="n"/>
+      <c r="E62" s="38">
+        <f>SUM(E32:E61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="14.25" customHeight="1" thickTop="1">
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="12" t="n"/>
+      <c r="E63" s="13" t="n"/>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="8" t="n"/>
+      <c r="H63" s="9" t="n"/>
+      <c r="I63" s="9" t="n"/>
+    </row>
+    <row r="64" ht="14.25" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Ich bitte um Überweisung des vorgenannten Rechnungsbetrages innerhalb von 14 Tagen.</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="14" t="n"/>
-      <c r="D60" s="14" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
-    </row>
-    <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="14" t="n"/>
-      <c r="D61" s="14" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="14" t="n"/>
+      <c r="D64" s="14" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
+    </row>
+    <row r="65" ht="14.25" customHeight="1">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="14" t="n"/>
+      <c r="D65" s="14" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
         <is>
           <t>Bank:</t>
         </is>
       </c>
-      <c r="B62" s="20" t="n"/>
-      <c r="C62" s="39" t="inlineStr">
+      <c r="B66" s="20" t="n"/>
+      <c r="C66" s="39" t="inlineStr">
         <is>
           <t>SumUp Limited</t>
         </is>
       </c>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
         <is>
           <t>IBAN:</t>
         </is>
       </c>
-      <c r="B63" s="20" t="n"/>
-      <c r="C63" s="40" t="inlineStr">
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="40" t="inlineStr">
         <is>
           <t>IE66SUMU99036512650081</t>
         </is>
       </c>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="10" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="6" t="n"/>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>Kontoinhaber:in:</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="41" t="inlineStr">
-        <is>
-          <t>Dominik Ballentin</t>
-        </is>
-      </c>
-      <c r="D64" s="12" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="6" t="n"/>
-      <c r="G64" s="6" t="n"/>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="3" t="n"/>
-    </row>
-    <row r="65">
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="6" t="n"/>
-      <c r="D65" s="54" t="n"/>
-      <c r="E65" s="57" t="n"/>
-      <c r="F65" s="6" t="n"/>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="3" t="n"/>
-      <c r="I65" s="3" t="n"/>
-    </row>
-    <row r="66">
-      <c r="D66" s="53" t="inlineStr">
-        <is>
-          <t>Unterschrift Honorarkraft</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="3" t="n"/>
-    </row>
-    <row r="67">
-      <c r="D67" s="53" t="n"/>
-      <c r="E67" s="53" t="n"/>
+      <c r="D67" s="12" t="n"/>
+      <c r="E67" s="10" t="n"/>
       <c r="F67" s="6" t="n"/>
       <c r="G67" s="6" t="n"/>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="D68" s="53" t="n"/>
-      <c r="E68" s="53" t="n"/>
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>Kontoinhaber:in:</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="41" t="inlineStr">
+        <is>
+          <t>Dominik Ballentin</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="n"/>
+      <c r="E68" s="10" t="n"/>
       <c r="F68" s="6" t="n"/>
       <c r="G68" s="6" t="n"/>
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="3" t="n"/>
     </row>
     <row r="69">
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="6" t="n"/>
       <c r="D69" s="53" t="n"/>
-      <c r="E69" s="53" t="n"/>
+      <c r="E69" s="56" t="n"/>
       <c r="F69" s="6" t="n"/>
       <c r="G69" s="6" t="n"/>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="6" t="n"/>
-      <c r="D70" s="1" t="n"/>
-      <c r="E70" s="12" t="n"/>
+      <c r="D70" s="33" t="n"/>
+      <c r="E70" s="33" t="n"/>
       <c r="F70" s="6" t="n"/>
       <c r="G70" s="6" t="n"/>
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="32" t="n"/>
-      <c r="B71" s="32" t="n"/>
-      <c r="C71" s="11" t="n"/>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="1" t="n"/>
+      <c r="E71" s="12" t="n"/>
+      <c r="F71" s="6" t="n"/>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="3" t="n"/>
+      <c r="I71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="34" t="inlineStr">
+      <c r="A72" s="32" t="n"/>
+      <c r="B72" s="32" t="n"/>
+      <c r="C72" s="11" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="34" t="inlineStr">
         <is>
           <t>sachlich und rechnerisch richtig</t>
         </is>
       </c>
-      <c r="B72" s="34" t="n"/>
-      <c r="C72" s="34" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="42" t="inlineStr">
+      <c r="B73" s="34" t="n"/>
+      <c r="C73" s="34" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="42" t="inlineStr">
         <is>
           <t>Unterschrift MA Pro Beruf GmbH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
+    <mergeCell ref="D69:E69"/>
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="G10:I10"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D65:E65"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>

--- a/output/Muster_Honorarrechnung-Lehrkräfte_March.xlsx
+++ b/output/Muster_Honorarrechnung-Lehrkräfte_March.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="497" windowWidth="22149" windowHeight="12600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="16920" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rechnungsvorlage Honorar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rechnungsvorlage Honorar'!$A$1:$E$79</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -753,19 +753,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3828125" defaultRowHeight="14.15" outlineLevelCol="0"/>
+  <dimension ref="A1:I78"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" outlineLevelCol="0"/>
   <cols>
-    <col width="15.07421875" customWidth="1" style="1" min="1" max="1"/>
-    <col width="20.69140625" customWidth="1" style="1" min="2" max="2"/>
-    <col width="53.3046875" customWidth="1" style="1" min="3" max="3"/>
-    <col width="14.69140625" customWidth="1" style="11" min="4" max="4"/>
+    <col width="15.140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="20.7109375" customWidth="1" style="1" min="2" max="2"/>
+    <col width="53.28515625" customWidth="1" style="1" min="3" max="3"/>
+    <col width="14.7109375" customWidth="1" style="11" min="4" max="4"/>
     <col width="14" customWidth="1" style="11" min="5" max="5"/>
-    <col width="11.15234375" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
-    <col width="9.84375" customWidth="1" style="1" min="7" max="7"/>
-    <col width="14.3828125" customWidth="1" style="1" min="8" max="8"/>
-    <col width="17.69140625" customWidth="1" style="1" min="9" max="9"/>
-    <col width="11.3828125" customWidth="1" style="1" min="10" max="16384"/>
+    <col width="11.140625" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="9.85546875" customWidth="1" style="1" min="7" max="7"/>
+    <col width="14.42578125" customWidth="1" style="1" min="8" max="8"/>
+    <col width="17.7109375" customWidth="1" style="1" min="9" max="9"/>
+    <col width="11.42578125" customWidth="1" style="1" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1013,7 +1013,7 @@
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="10" t="n"/>
     </row>
-    <row r="29" ht="34.4" customHeight="1">
+    <row r="29" ht="34.35" customHeight="1">
       <c r="A29" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">für die unten aufgeführten Leistungen für den Stütz- und Förderunterricht in der Ausbildungsassistenz im Projekt Assistierte Ausbildung AsA VIII berechne ich Ihnen wie folgt: </t>
@@ -1025,7 +1025,7 @@
       <c r="D30" s="10" t="n"/>
       <c r="E30" s="10" t="n"/>
     </row>
-    <row r="31" ht="42.45" customHeight="1">
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="35" t="inlineStr">
         <is>
           <t>Datum</t>
@@ -1495,7 +1495,7 @@
     <row r="52">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>23.03.2026</t>
+          <t>22.03.2026</t>
         </is>
       </c>
       <c r="B52" s="21" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+          <t>Vorbereitung für Unterricht 0,75 Stunden</t>
         </is>
       </c>
       <c r="D52" s="23" t="n">
@@ -1517,7 +1517,7 @@
     <row r="53">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>24.03.2026</t>
+          <t>23.03.2026</t>
         </is>
       </c>
       <c r="B53" s="21" t="n">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Unterricht ASA 8 Vertretung</t>
+          <t>Unterricht ASA 9 Vertretung</t>
         </is>
       </c>
       <c r="D53" s="23" t="n">
@@ -1539,7 +1539,7 @@
     <row r="54">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>25.03.2026</t>
+          <t>23.03.2026</t>
         </is>
       </c>
       <c r="B54" s="21" t="n">
@@ -1561,7 +1561,7 @@
     <row r="55">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>26.03.2026</t>
+          <t>24.03.2026</t>
         </is>
       </c>
       <c r="B55" s="21" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C55" s="22" t="inlineStr">
         <is>
-          <t>Unterricht ASA 8</t>
+          <t>Unterricht ASA 8 Vertretung</t>
         </is>
       </c>
       <c r="D55" s="23" t="n">
@@ -1583,7 +1583,7 @@
     <row r="56">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>30.03.2026</t>
+          <t>24.03.2026</t>
         </is>
       </c>
       <c r="B56" s="21" t="n">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+          <t>Vorbereitung für Unterricht 0,75 Stunden</t>
         </is>
       </c>
       <c r="D56" s="23" t="n">
@@ -1605,7 +1605,7 @@
     <row r="57">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>31.03.2026</t>
+          <t>25.03.2026</t>
         </is>
       </c>
       <c r="B57" s="21" t="n">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C57" s="22" t="inlineStr">
         <is>
-          <t>Unterricht ASA 8 Vertretung</t>
+          <t>Unterricht ASA 9 Vertretung</t>
         </is>
       </c>
       <c r="D57" s="23" t="n">
@@ -1625,193 +1625,317 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="44" t="n"/>
-      <c r="B58" s="21" t="n"/>
-      <c r="C58" s="22" t="n"/>
-      <c r="D58" s="23" t="n"/>
+      <c r="A58" s="44" t="inlineStr">
+        <is>
+          <t>25.03.2026</t>
+        </is>
+      </c>
+      <c r="B58" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>19</v>
+      </c>
       <c r="E58" s="37">
         <f>ROUND(B58*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="44" t="n"/>
-      <c r="B59" s="21" t="n"/>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="23" t="n"/>
+      <c r="A59" s="44" t="inlineStr">
+        <is>
+          <t>26.03.2026</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" s="22" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="n">
+        <v>19</v>
+      </c>
       <c r="E59" s="37">
         <f>ROUND(B59*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="44" t="n"/>
-      <c r="B60" s="21" t="n"/>
-      <c r="C60" s="22" t="n"/>
-      <c r="D60" s="23" t="n"/>
+      <c r="A60" s="44" t="inlineStr">
+        <is>
+          <t>26.03.2026</t>
+        </is>
+      </c>
+      <c r="B60" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C60" s="22" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>19</v>
+      </c>
       <c r="E60" s="37">
         <f>ROUND(B60*$D$32,2)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="44" t="n"/>
-      <c r="B61" s="21" t="n"/>
-      <c r="C61" s="22" t="n"/>
-      <c r="D61" s="23" t="n"/>
+      <c r="A61" s="44" t="inlineStr">
+        <is>
+          <t>27.03.2026</t>
+        </is>
+      </c>
+      <c r="B61" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" s="22" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 9 Vertretung</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="n">
+        <v>19</v>
+      </c>
       <c r="E61" s="37">
         <f>ROUND(B61*$D$32,2)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="14.6" customFormat="1" customHeight="1" s="7" thickBot="1">
-      <c r="A62" s="50" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="44" t="inlineStr">
+        <is>
+          <t>30.03.2026</t>
+        </is>
+      </c>
+      <c r="B62" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C62" s="22" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht: 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E62" s="37">
+        <f>ROUND(B62*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="44" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B63" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="22" t="inlineStr">
+        <is>
+          <t>Unterricht ASA 8 Vertretung</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E63" s="37">
+        <f>ROUND(B63*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="44" t="inlineStr">
+        <is>
+          <t>31.03.2026</t>
+        </is>
+      </c>
+      <c r="B64" s="21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C64" s="22" t="inlineStr">
+        <is>
+          <t>Vorbereitung für Unterricht 0,75 Stunden</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="E64" s="37">
+        <f>ROUND(B64*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="44" t="n"/>
+      <c r="B65" s="21" t="n"/>
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="23" t="n"/>
+      <c r="E65" s="37">
+        <f>ROUND(B65*$D$32,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customFormat="1" customHeight="1" s="7" thickBot="1">
+      <c r="A66" s="50" t="inlineStr">
         <is>
           <t>Gesamtbetrag</t>
         </is>
       </c>
-      <c r="B62" s="55" t="n"/>
-      <c r="C62" s="55" t="n"/>
-      <c r="D62" s="24" t="n"/>
-      <c r="E62" s="38">
-        <f>SUM(E32:E61)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="14.25" customHeight="1" thickTop="1">
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="13" t="n"/>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="9" t="n"/>
-      <c r="I63" s="9" t="n"/>
-    </row>
-    <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="B66" s="55" t="n"/>
+      <c r="C66" s="55" t="n"/>
+      <c r="D66" s="24" t="n"/>
+      <c r="E66" s="38">
+        <f>SUM(E32:E65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="14.25" customHeight="1" thickTop="1">
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="12" t="n"/>
+      <c r="E67" s="13" t="n"/>
+      <c r="F67" s="8" t="n"/>
+      <c r="G67" s="8" t="n"/>
+      <c r="H67" s="9" t="n"/>
+      <c r="I67" s="9" t="n"/>
+    </row>
+    <row r="68" ht="14.25" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Ich bitte um Überweisung des vorgenannten Rechnungsbetrages innerhalb von 14 Tagen.</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="14" t="n"/>
-      <c r="D64" s="14" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="n"/>
-    </row>
-    <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="14" t="n"/>
-      <c r="D65" s="14" t="n"/>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="14" t="n"/>
+      <c r="D68" s="14" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+    </row>
+    <row r="69" ht="14.25" customHeight="1">
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="14" t="n"/>
+      <c r="D69" s="14" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
         <is>
           <t>Bank:</t>
         </is>
       </c>
-      <c r="B66" s="20" t="n"/>
-      <c r="C66" s="39" t="inlineStr">
+      <c r="B70" s="20" t="n"/>
+      <c r="C70" s="39" t="inlineStr">
         <is>
           <t>SumUp Limited</t>
         </is>
       </c>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n"/>
-      <c r="G66" s="3" t="n"/>
-      <c r="H66" s="3" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
         <is>
           <t>IBAN:</t>
         </is>
       </c>
-      <c r="B67" s="20" t="n"/>
-      <c r="C67" s="40" t="inlineStr">
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="40" t="inlineStr">
         <is>
           <t>IE66SUMU99036512650081</t>
         </is>
       </c>
-      <c r="D67" s="12" t="n"/>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="6" t="n"/>
-      <c r="G67" s="6" t="n"/>
-      <c r="H67" s="3" t="n"/>
-      <c r="I67" s="3" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>Kontoinhaber:in:</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="41" t="inlineStr">
-        <is>
-          <t>Dominik Ballentin</t>
-        </is>
-      </c>
-      <c r="D68" s="12" t="n"/>
-      <c r="E68" s="10" t="n"/>
-      <c r="F68" s="6" t="n"/>
-      <c r="G68" s="6" t="n"/>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
-    </row>
-    <row r="69">
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="53" t="n"/>
-      <c r="E69" s="56" t="n"/>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="3" t="n"/>
-      <c r="I69" s="3" t="n"/>
-    </row>
-    <row r="70">
-      <c r="D70" s="33" t="n"/>
-      <c r="E70" s="33" t="n"/>
-      <c r="F70" s="6" t="n"/>
-      <c r="G70" s="6" t="n"/>
-      <c r="H70" s="3" t="n"/>
-      <c r="I70" s="3" t="n"/>
-    </row>
-    <row r="71">
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="1" t="n"/>
-      <c r="E71" s="12" t="n"/>
+      <c r="D71" s="12" t="n"/>
+      <c r="E71" s="10" t="n"/>
       <c r="F71" s="6" t="n"/>
       <c r="G71" s="6" t="n"/>
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="32" t="n"/>
-      <c r="B72" s="32" t="n"/>
-      <c r="C72" s="11" t="n"/>
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>Kontoinhaber:in:</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="41" t="inlineStr">
+        <is>
+          <t>Dominik Ballentin</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="6" t="n"/>
+      <c r="G72" s="6" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="34" t="inlineStr">
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="53" t="n"/>
+      <c r="E73" s="56" t="n"/>
+      <c r="F73" s="6" t="n"/>
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="D74" s="33" t="n"/>
+      <c r="E74" s="33" t="n"/>
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="6" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="1" t="n"/>
+      <c r="E75" s="12" t="n"/>
+      <c r="F75" s="6" t="n"/>
+      <c r="G75" s="6" t="n"/>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="32" t="n"/>
+      <c r="B76" s="32" t="n"/>
+      <c r="C76" s="11" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="34" t="inlineStr">
         <is>
           <t>sachlich und rechnerisch richtig</t>
         </is>
       </c>
-      <c r="B73" s="34" t="n"/>
-      <c r="C73" s="34" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="42" t="inlineStr">
+      <c r="B77" s="34" t="n"/>
+      <c r="C77" s="34" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="42" t="inlineStr">
         <is>
           <t>Unterschrift MA Pro Beruf GmbH</t>
         </is>
@@ -1819,18 +1943,18 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D69:E69"/>
     <mergeCell ref="G24:I24"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="G10:I10"/>
-    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="D73:E73"/>
     <mergeCell ref="G9:H9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.984251968503937" right="0.7874015748031497" top="0.984251968503937" bottom="0.7874015748031497" header="0.5118110236220472" footer="0.5118110236220472"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="74"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="62"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="5" min="0" max="51" man="1"/>
   </colBreaks>
